--- a/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 2.xlsx
+++ b/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 2.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Tiketing 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Tiketing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC1C16C-D858-490E-8541-2A1AA3278419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7mh54Bje8eDJzRIWFZnqnVBd7Yudwg=="/>
@@ -144,7 +143,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -638,7 +637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB59F0C-99EC-470D-9B5F-D84C9B507A36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -770,10 +769,22 @@
       <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16"/>
+      <c r="D5" s="15" t="str">
+        <f>VLOOKUP(LEFT(C5,2),$I$4:$O$7,2,FALSE)</f>
+        <v>GARUDA</v>
+      </c>
+      <c r="E5" s="15" t="str">
+        <f>INDEX($L$4:$L$7,MATCH(MID(C5,4,3),$K$4:$K$7,0))</f>
+        <v>JAKARTA</v>
+      </c>
+      <c r="F5" s="15" t="str">
+        <f>HLOOKUP(RIGHT(C5,2),$I$9:$M$10,2,FALSE)</f>
+        <v>11 AM</v>
+      </c>
+      <c r="G5" s="16">
+        <f>INDEX($L$4:$O$7,MATCH(E5,$L$4:$L$7,0),MATCH(D5,$L$4:$O$4,0))</f>
+        <v>220000</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="11" t="s">
         <v>33</v>
@@ -805,10 +816,22 @@
       <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="16"/>
+      <c r="D6" s="15" t="str">
+        <f t="shared" ref="D6:D11" si="0">VLOOKUP(LEFT(C6,2),$I$4:$O$7,2,FALSE)</f>
+        <v>MERPATI</v>
+      </c>
+      <c r="E6" s="15" t="str">
+        <f t="shared" ref="E6:E11" si="1">INDEX($L$4:$L$7,MATCH(MID(C6,4,3),$K$4:$K$7,0))</f>
+        <v>SURABAYA</v>
+      </c>
+      <c r="F6" s="15" t="str">
+        <f t="shared" ref="F6:F11" si="2">HLOOKUP(RIGHT(C6,2),$I$9:$M$10,2,FALSE)</f>
+        <v>5 AM</v>
+      </c>
+      <c r="G6" s="16">
+        <f t="shared" ref="G6:G11" si="3">INDEX($L$4:$O$7,MATCH(E6,$L$4:$L$7,0),MATCH(D6,$L$4:$O$4,0))</f>
+        <v>380000</v>
+      </c>
       <c r="H6" s="1"/>
       <c r="I6" s="11" t="s">
         <v>15</v>
@@ -840,10 +863,22 @@
       <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="16"/>
+      <c r="D7" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>GARUDA</v>
+      </c>
+      <c r="E7" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>MEDAN</v>
+      </c>
+      <c r="F7" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>11 AM</v>
+      </c>
+      <c r="G7" s="16">
+        <f t="shared" si="3"/>
+        <v>625000</v>
+      </c>
       <c r="H7" s="1"/>
       <c r="I7" s="11" t="s">
         <v>19</v>
@@ -875,10 +910,22 @@
       <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>MERPATI</v>
+      </c>
+      <c r="E8" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>JAKARTA</v>
+      </c>
+      <c r="F8" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>5 AM</v>
+      </c>
+      <c r="G8" s="16">
+        <f t="shared" si="3"/>
+        <v>210000</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="4"/>
       <c r="J8" s="1"/>
@@ -896,10 +943,22 @@
       <c r="C9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>LION</v>
+      </c>
+      <c r="E9" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>SURABAYA</v>
+      </c>
+      <c r="F9" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>3 AM</v>
+      </c>
+      <c r="G9" s="16">
+        <f t="shared" si="3"/>
+        <v>370000</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="20" t="s">
         <v>23</v>
@@ -925,10 +984,22 @@
       <c r="C10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>MERPATI</v>
+      </c>
+      <c r="E10" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>MEDAN</v>
+      </c>
+      <c r="F10" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>5 AM</v>
+      </c>
+      <c r="G10" s="16">
+        <f t="shared" si="3"/>
+        <v>590000</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="22" t="s">
         <v>5</v>
@@ -954,10 +1025,22 @@
       <c r="C11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>LION</v>
+      </c>
+      <c r="E11" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>MEDAN</v>
+      </c>
+      <c r="F11" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>5 AM</v>
+      </c>
+      <c r="G11" s="16">
+        <f t="shared" si="3"/>
+        <v>575000</v>
+      </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -3944,7 +4027,7 @@
     <mergeCell ref="J1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{FB0F47BD-B1C5-4B05-A866-B5623B1F89EB}"/>
+    <hyperlink ref="J2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 2.xlsx
+++ b/exercise/Admin/Admin Tiketing/Tes Excel Admin Tiketing 2.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Tiketing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Tiketing 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC1C16C-D858-490E-8541-2A1AA3278419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7mh54Bje8eDJzRIWFZnqnVBd7Yudwg=="/>
@@ -143,7 +144,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -637,7 +638,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB59F0C-99EC-470D-9B5F-D84C9B507A36}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -769,22 +770,10 @@
       <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="15" t="str">
-        <f>VLOOKUP(LEFT(C5,2),$I$4:$O$7,2,FALSE)</f>
-        <v>GARUDA</v>
-      </c>
-      <c r="E5" s="15" t="str">
-        <f>INDEX($L$4:$L$7,MATCH(MID(C5,4,3),$K$4:$K$7,0))</f>
-        <v>JAKARTA</v>
-      </c>
-      <c r="F5" s="15" t="str">
-        <f>HLOOKUP(RIGHT(C5,2),$I$9:$M$10,2,FALSE)</f>
-        <v>11 AM</v>
-      </c>
-      <c r="G5" s="16">
-        <f>INDEX($L$4:$O$7,MATCH(E5,$L$4:$L$7,0),MATCH(D5,$L$4:$O$4,0))</f>
-        <v>220000</v>
-      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="16"/>
       <c r="H5" s="1"/>
       <c r="I5" s="11" t="s">
         <v>33</v>
@@ -816,22 +805,10 @@
       <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="15" t="str">
-        <f t="shared" ref="D6:D11" si="0">VLOOKUP(LEFT(C6,2),$I$4:$O$7,2,FALSE)</f>
-        <v>MERPATI</v>
-      </c>
-      <c r="E6" s="15" t="str">
-        <f t="shared" ref="E6:E11" si="1">INDEX($L$4:$L$7,MATCH(MID(C6,4,3),$K$4:$K$7,0))</f>
-        <v>SURABAYA</v>
-      </c>
-      <c r="F6" s="15" t="str">
-        <f t="shared" ref="F6:F11" si="2">HLOOKUP(RIGHT(C6,2),$I$9:$M$10,2,FALSE)</f>
-        <v>5 AM</v>
-      </c>
-      <c r="G6" s="16">
-        <f t="shared" ref="G6:G11" si="3">INDEX($L$4:$O$7,MATCH(E6,$L$4:$L$7,0),MATCH(D6,$L$4:$O$4,0))</f>
-        <v>380000</v>
-      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16"/>
       <c r="H6" s="1"/>
       <c r="I6" s="11" t="s">
         <v>15</v>
@@ -863,22 +840,10 @@
       <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>GARUDA</v>
-      </c>
-      <c r="E7" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>MEDAN</v>
-      </c>
-      <c r="F7" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>11 AM</v>
-      </c>
-      <c r="G7" s="16">
-        <f t="shared" si="3"/>
-        <v>625000</v>
-      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="16"/>
       <c r="H7" s="1"/>
       <c r="I7" s="11" t="s">
         <v>19</v>
@@ -910,22 +875,10 @@
       <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>MERPATI</v>
-      </c>
-      <c r="E8" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>JAKARTA</v>
-      </c>
-      <c r="F8" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>5 AM</v>
-      </c>
-      <c r="G8" s="16">
-        <f t="shared" si="3"/>
-        <v>210000</v>
-      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
       <c r="H8" s="1"/>
       <c r="I8" s="4"/>
       <c r="J8" s="1"/>
@@ -943,22 +896,10 @@
       <c r="C9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>LION</v>
-      </c>
-      <c r="E9" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>SURABAYA</v>
-      </c>
-      <c r="F9" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>3 AM</v>
-      </c>
-      <c r="G9" s="16">
-        <f t="shared" si="3"/>
-        <v>370000</v>
-      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
       <c r="H9" s="1"/>
       <c r="I9" s="20" t="s">
         <v>23</v>
@@ -984,22 +925,10 @@
       <c r="C10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>MERPATI</v>
-      </c>
-      <c r="E10" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>MEDAN</v>
-      </c>
-      <c r="F10" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>5 AM</v>
-      </c>
-      <c r="G10" s="16">
-        <f t="shared" si="3"/>
-        <v>590000</v>
-      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
       <c r="H10" s="1"/>
       <c r="I10" s="22" t="s">
         <v>5</v>
@@ -1025,22 +954,10 @@
       <c r="C11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>LION</v>
-      </c>
-      <c r="E11" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>MEDAN</v>
-      </c>
-      <c r="F11" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>5 AM</v>
-      </c>
-      <c r="G11" s="16">
-        <f t="shared" si="3"/>
-        <v>575000</v>
-      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -4027,7 +3944,7 @@
     <mergeCell ref="J1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1"/>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{FB0F47BD-B1C5-4B05-A866-B5623B1F89EB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
